--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -1452,50 +1452,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126023914</v>
+        <v>126023940</v>
       </c>
       <c r="B10" t="n">
-        <v>56843</v>
+        <v>78968</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482148</v>
+        <v>482101</v>
       </c>
       <c r="R10" t="n">
-        <v>6951652</v>
+        <v>6951693</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1554,45 +1549,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126023940</v>
+        <v>126023914</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>56843</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482101</v>
+        <v>482148</v>
       </c>
       <c r="R11" t="n">
-        <v>6951693</v>
+        <v>6951652</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1748,10 +1748,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126023920</v>
+        <v>126023926</v>
       </c>
       <c r="B13" t="n">
-        <v>78727</v>
+        <v>80071</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1759,21 +1759,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>482158</v>
+        <v>482123</v>
       </c>
       <c r="R13" t="n">
-        <v>6951891</v>
+        <v>6951876</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1845,10 +1845,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126023926</v>
+        <v>126023920</v>
       </c>
       <c r="B14" t="n">
-        <v>80071</v>
+        <v>78727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1856,21 +1856,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482123</v>
+        <v>482158</v>
       </c>
       <c r="R14" t="n">
-        <v>6951876</v>
+        <v>6951891</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2330,10 +2330,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126023921</v>
+        <v>126023946</v>
       </c>
       <c r="B19" t="n">
-        <v>78727</v>
+        <v>78635</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2341,21 +2341,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>482156</v>
+        <v>482039</v>
       </c>
       <c r="R19" t="n">
-        <v>6951883</v>
+        <v>6951778</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126023946</v>
+        <v>126023921</v>
       </c>
       <c r="B20" t="n">
-        <v>78635</v>
+        <v>78727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>482039</v>
+        <v>482156</v>
       </c>
       <c r="R20" t="n">
-        <v>6951778</v>
+        <v>6951883</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2524,57 +2524,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126023938</v>
+        <v>126023925</v>
       </c>
       <c r="B21" t="n">
-        <v>98332</v>
+        <v>80071</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>482167</v>
+        <v>482111</v>
       </c>
       <c r="R21" t="n">
-        <v>6951805</v>
+        <v>6951916</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2615,7 +2603,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2634,7 +2621,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126023925</v>
+        <v>126023929</v>
       </c>
       <c r="B22" t="n">
         <v>80071</v>
@@ -2669,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>482111</v>
+        <v>481977</v>
       </c>
       <c r="R22" t="n">
-        <v>6951916</v>
+        <v>6951858</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2731,45 +2718,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126023929</v>
+        <v>126023938</v>
       </c>
       <c r="B23" t="n">
-        <v>80071</v>
+        <v>98334</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481977</v>
+        <v>482167</v>
       </c>
       <c r="R23" t="n">
-        <v>6951858</v>
+        <v>6951805</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2810,6 +2809,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126023947</v>
+        <v>126023939</v>
       </c>
       <c r="B27" t="n">
-        <v>78635</v>
+        <v>78968</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3130,21 +3130,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>482066</v>
+        <v>482162</v>
       </c>
       <c r="R27" t="n">
-        <v>6951791</v>
+        <v>6951763</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126023939</v>
+        <v>126023947</v>
       </c>
       <c r="B28" t="n">
-        <v>78968</v>
+        <v>78635</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3227,21 +3227,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>482162</v>
+        <v>482066</v>
       </c>
       <c r="R28" t="n">
-        <v>6951763</v>
+        <v>6951791</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -2524,45 +2524,57 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126023925</v>
+        <v>126023938</v>
       </c>
       <c r="B21" t="n">
-        <v>80071</v>
+        <v>98334</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>482111</v>
+        <v>482167</v>
       </c>
       <c r="R21" t="n">
-        <v>6951916</v>
+        <v>6951805</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2603,6 +2615,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2621,7 +2634,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126023929</v>
+        <v>126023925</v>
       </c>
       <c r="B22" t="n">
         <v>80071</v>
@@ -2656,10 +2669,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481977</v>
+        <v>482111</v>
       </c>
       <c r="R22" t="n">
-        <v>6951858</v>
+        <v>6951916</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2718,57 +2731,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126023938</v>
+        <v>126023929</v>
       </c>
       <c r="B23" t="n">
-        <v>98334</v>
+        <v>80071</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>482167</v>
+        <v>481977</v>
       </c>
       <c r="R23" t="n">
-        <v>6951805</v>
+        <v>6951858</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,7 +2810,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126023941</v>
       </c>
       <c r="B2" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126023950</v>
       </c>
       <c r="B3" t="n">
-        <v>78374</v>
+        <v>78378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>126023916</v>
       </c>
       <c r="B4" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>126023949</v>
       </c>
       <c r="B5" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>126023932</v>
       </c>
       <c r="B6" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>126023917</v>
       </c>
       <c r="B7" t="n">
-        <v>80099</v>
+        <v>80103</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>126023927</v>
       </c>
       <c r="B8" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>126023948</v>
       </c>
       <c r="B9" t="n">
-        <v>77917</v>
+        <v>77921</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1452,45 +1452,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126023940</v>
+        <v>126023914</v>
       </c>
       <c r="B10" t="n">
-        <v>78968</v>
+        <v>56843</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482101</v>
+        <v>482148</v>
       </c>
       <c r="R10" t="n">
-        <v>6951693</v>
+        <v>6951652</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,50 +1554,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126023914</v>
+        <v>126023940</v>
       </c>
       <c r="B11" t="n">
-        <v>56843</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482148</v>
+        <v>482101</v>
       </c>
       <c r="R11" t="n">
-        <v>6951652</v>
+        <v>6951693</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126023934</v>
+        <v>126023920</v>
       </c>
       <c r="B12" t="n">
-        <v>80071</v>
+        <v>78731</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1662,21 +1662,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482030</v>
+        <v>482158</v>
       </c>
       <c r="R12" t="n">
-        <v>6951824</v>
+        <v>6951891</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,10 +1748,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126023926</v>
+        <v>126023934</v>
       </c>
       <c r="B13" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>482123</v>
+        <v>482030</v>
       </c>
       <c r="R13" t="n">
-        <v>6951876</v>
+        <v>6951824</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1845,10 +1845,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126023920</v>
+        <v>126023926</v>
       </c>
       <c r="B14" t="n">
-        <v>78727</v>
+        <v>80075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1856,21 +1856,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482158</v>
+        <v>482123</v>
       </c>
       <c r="R14" t="n">
-        <v>6951891</v>
+        <v>6951876</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1945,7 +1945,7 @@
         <v>126023931</v>
       </c>
       <c r="B15" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>126023933</v>
       </c>
       <c r="B16" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>126023956</v>
       </c>
       <c r="B17" t="n">
-        <v>77917</v>
+        <v>77921</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>126023923</v>
       </c>
       <c r="B18" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2330,10 +2330,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126023946</v>
+        <v>126023921</v>
       </c>
       <c r="B19" t="n">
-        <v>78635</v>
+        <v>78731</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2341,21 +2341,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>482039</v>
+        <v>482156</v>
       </c>
       <c r="R19" t="n">
-        <v>6951778</v>
+        <v>6951883</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126023921</v>
+        <v>126023946</v>
       </c>
       <c r="B20" t="n">
-        <v>78727</v>
+        <v>78639</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>482156</v>
+        <v>482039</v>
       </c>
       <c r="R20" t="n">
-        <v>6951883</v>
+        <v>6951778</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2527,7 +2527,7 @@
         <v>126023938</v>
       </c>
       <c r="B21" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>126023925</v>
       </c>
       <c r="B22" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>126023929</v>
       </c>
       <c r="B23" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>126023958</v>
       </c>
       <c r="B24" t="n">
-        <v>77917</v>
+        <v>77921</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>126023922</v>
       </c>
       <c r="B25" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>126023924</v>
       </c>
       <c r="B26" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>126023939</v>
       </c>
       <c r="B27" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>126023947</v>
       </c>
       <c r="B28" t="n">
-        <v>78635</v>
+        <v>78639</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>126023928</v>
       </c>
       <c r="B29" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>126023937</v>
       </c>
       <c r="B30" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -1651,10 +1651,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126023920</v>
+        <v>126023934</v>
       </c>
       <c r="B12" t="n">
-        <v>78731</v>
+        <v>80075</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1662,21 +1662,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482158</v>
+        <v>482030</v>
       </c>
       <c r="R12" t="n">
-        <v>6951891</v>
+        <v>6951824</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,7 +1748,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126023934</v>
+        <v>126023926</v>
       </c>
       <c r="B13" t="n">
         <v>80075</v>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>482030</v>
+        <v>482123</v>
       </c>
       <c r="R13" t="n">
-        <v>6951824</v>
+        <v>6951876</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1845,10 +1845,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126023926</v>
+        <v>126023920</v>
       </c>
       <c r="B14" t="n">
-        <v>80075</v>
+        <v>78731</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1856,21 +1856,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482123</v>
+        <v>482158</v>
       </c>
       <c r="R14" t="n">
-        <v>6951876</v>
+        <v>6951891</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -1651,10 +1651,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126023934</v>
+        <v>126023920</v>
       </c>
       <c r="B12" t="n">
-        <v>80075</v>
+        <v>78731</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1662,21 +1662,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482030</v>
+        <v>482158</v>
       </c>
       <c r="R12" t="n">
-        <v>6951824</v>
+        <v>6951891</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,7 +1748,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126023926</v>
+        <v>126023934</v>
       </c>
       <c r="B13" t="n">
         <v>80075</v>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>482123</v>
+        <v>482030</v>
       </c>
       <c r="R13" t="n">
-        <v>6951876</v>
+        <v>6951824</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1845,10 +1845,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126023920</v>
+        <v>126023926</v>
       </c>
       <c r="B14" t="n">
-        <v>78731</v>
+        <v>80075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1856,21 +1856,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482158</v>
+        <v>482123</v>
       </c>
       <c r="R14" t="n">
-        <v>6951891</v>
+        <v>6951876</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126023933</v>
+        <v>126023956</v>
       </c>
       <c r="B16" t="n">
-        <v>80075</v>
+        <v>77921</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2050,21 +2050,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>482027</v>
+        <v>482150</v>
       </c>
       <c r="R16" t="n">
-        <v>6951842</v>
+        <v>6951653</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2136,10 +2136,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126023956</v>
+        <v>126023933</v>
       </c>
       <c r="B17" t="n">
-        <v>77921</v>
+        <v>80075</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2147,21 +2147,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>482150</v>
+        <v>482027</v>
       </c>
       <c r="R17" t="n">
-        <v>6951653</v>
+        <v>6951842</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2330,10 +2330,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126023921</v>
+        <v>126023946</v>
       </c>
       <c r="B19" t="n">
-        <v>78731</v>
+        <v>78639</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2341,21 +2341,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>482156</v>
+        <v>482039</v>
       </c>
       <c r="R19" t="n">
-        <v>6951883</v>
+        <v>6951778</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126023946</v>
+        <v>126023921</v>
       </c>
       <c r="B20" t="n">
-        <v>78639</v>
+        <v>78731</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>482039</v>
+        <v>482156</v>
       </c>
       <c r="R20" t="n">
-        <v>6951778</v>
+        <v>6951883</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2524,57 +2524,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126023938</v>
+        <v>126023925</v>
       </c>
       <c r="B21" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>482167</v>
+        <v>482111</v>
       </c>
       <c r="R21" t="n">
-        <v>6951805</v>
+        <v>6951916</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2615,7 +2603,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2634,7 +2621,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126023925</v>
+        <v>126023929</v>
       </c>
       <c r="B22" t="n">
         <v>80075</v>
@@ -2669,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>482111</v>
+        <v>481977</v>
       </c>
       <c r="R22" t="n">
-        <v>6951916</v>
+        <v>6951858</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2731,45 +2718,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126023929</v>
+        <v>126023938</v>
       </c>
       <c r="B23" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481977</v>
+        <v>482167</v>
       </c>
       <c r="R23" t="n">
-        <v>6951858</v>
+        <v>6951805</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2810,6 +2809,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126023924</v>
+        <v>126023947</v>
       </c>
       <c r="B26" t="n">
-        <v>80075</v>
+        <v>78639</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>482164</v>
+        <v>482066</v>
       </c>
       <c r="R26" t="n">
-        <v>6951793</v>
+        <v>6951791</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126023947</v>
+        <v>126023924</v>
       </c>
       <c r="B28" t="n">
-        <v>78639</v>
+        <v>80075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3227,21 +3227,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>482066</v>
+        <v>482164</v>
       </c>
       <c r="R28" t="n">
-        <v>6951791</v>
+        <v>6951793</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126023950</v>
+        <v>126023916</v>
       </c>
       <c r="B3" t="n">
-        <v>78378</v>
+        <v>80104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482058</v>
+        <v>482137</v>
       </c>
       <c r="R3" t="n">
-        <v>6951794</v>
+        <v>6951852</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -870,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126023916</v>
+        <v>126023949</v>
       </c>
       <c r="B4" t="n">
-        <v>80104</v>
+        <v>79561</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -905,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482137</v>
+        <v>482058</v>
       </c>
       <c r="R4" t="n">
-        <v>6951852</v>
+        <v>6951794</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126023949</v>
+        <v>126023950</v>
       </c>
       <c r="B5" t="n">
-        <v>79561</v>
+        <v>78378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -978,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,6 +1045,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126023947</v>
+        <v>126023939</v>
       </c>
       <c r="B26" t="n">
-        <v>78639</v>
+        <v>78972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>482066</v>
+        <v>482162</v>
       </c>
       <c r="R26" t="n">
-        <v>6951791</v>
+        <v>6951763</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126023939</v>
+        <v>126023947</v>
       </c>
       <c r="B27" t="n">
-        <v>78972</v>
+        <v>78639</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3130,21 +3130,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>482162</v>
+        <v>482066</v>
       </c>
       <c r="R27" t="n">
-        <v>6951763</v>
+        <v>6951791</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126023916</v>
+        <v>126023950</v>
       </c>
       <c r="B3" t="n">
-        <v>80104</v>
+        <v>78378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482137</v>
+        <v>482058</v>
       </c>
       <c r="R3" t="n">
-        <v>6951852</v>
+        <v>6951794</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,6 +851,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -869,32 +870,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126023949</v>
+        <v>126023916</v>
       </c>
       <c r="B4" t="n">
-        <v>79561</v>
+        <v>80104</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482058</v>
+        <v>482137</v>
       </c>
       <c r="R4" t="n">
-        <v>6951794</v>
+        <v>6951852</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126023950</v>
+        <v>126023949</v>
       </c>
       <c r="B5" t="n">
-        <v>78378</v>
+        <v>79561</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,7 +1046,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1452,50 +1452,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126023914</v>
+        <v>126023940</v>
       </c>
       <c r="B10" t="n">
-        <v>56843</v>
+        <v>78972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482148</v>
+        <v>482101</v>
       </c>
       <c r="R10" t="n">
-        <v>6951652</v>
+        <v>6951693</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1554,45 +1549,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126023940</v>
+        <v>126023914</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>56843</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482101</v>
+        <v>482148</v>
       </c>
       <c r="R11" t="n">
-        <v>6951693</v>
+        <v>6951652</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2621,45 +2621,57 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126023929</v>
+        <v>126023938</v>
       </c>
       <c r="B22" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481977</v>
+        <v>482167</v>
       </c>
       <c r="R22" t="n">
-        <v>6951858</v>
+        <v>6951805</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2700,6 +2712,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2718,57 +2731,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126023938</v>
+        <v>126023929</v>
       </c>
       <c r="B23" t="n">
-        <v>98339</v>
+        <v>80075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>482167</v>
+        <v>481977</v>
       </c>
       <c r="R23" t="n">
-        <v>6951805</v>
+        <v>6951858</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,7 +2810,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126023939</v>
+        <v>126023947</v>
       </c>
       <c r="B26" t="n">
-        <v>78972</v>
+        <v>78639</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>482162</v>
+        <v>482066</v>
       </c>
       <c r="R26" t="n">
-        <v>6951763</v>
+        <v>6951791</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126023947</v>
+        <v>126023939</v>
       </c>
       <c r="B27" t="n">
-        <v>78639</v>
+        <v>78972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3130,21 +3130,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>482066</v>
+        <v>482162</v>
       </c>
       <c r="R27" t="n">
-        <v>6951791</v>
+        <v>6951763</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126023941</v>
       </c>
       <c r="B2" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126023950</v>
+        <v>126023916</v>
       </c>
       <c r="B3" t="n">
-        <v>78378</v>
+        <v>80105</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482058</v>
+        <v>482137</v>
       </c>
       <c r="R3" t="n">
-        <v>6951794</v>
+        <v>6951852</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -870,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126023916</v>
+        <v>126023949</v>
       </c>
       <c r="B4" t="n">
-        <v>80104</v>
+        <v>79562</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -905,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482137</v>
+        <v>482058</v>
       </c>
       <c r="R4" t="n">
-        <v>6951852</v>
+        <v>6951794</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126023949</v>
+        <v>126023950</v>
       </c>
       <c r="B5" t="n">
-        <v>79561</v>
+        <v>78379</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -978,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,6 +1045,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1067,7 +1067,7 @@
         <v>126023932</v>
       </c>
       <c r="B6" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>126023917</v>
       </c>
       <c r="B7" t="n">
-        <v>80103</v>
+        <v>80104</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>126023927</v>
       </c>
       <c r="B8" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>126023948</v>
       </c>
       <c r="B9" t="n">
-        <v>77921</v>
+        <v>77922</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1452,45 +1452,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126023940</v>
+        <v>126023914</v>
       </c>
       <c r="B10" t="n">
-        <v>78972</v>
+        <v>56844</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482101</v>
+        <v>482148</v>
       </c>
       <c r="R10" t="n">
-        <v>6951693</v>
+        <v>6951652</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,50 +1554,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126023914</v>
+        <v>126023940</v>
       </c>
       <c r="B11" t="n">
-        <v>56843</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482148</v>
+        <v>482101</v>
       </c>
       <c r="R11" t="n">
-        <v>6951652</v>
+        <v>6951693</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126023920</v>
+        <v>126023934</v>
       </c>
       <c r="B12" t="n">
-        <v>78731</v>
+        <v>80076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1662,21 +1662,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482158</v>
+        <v>482030</v>
       </c>
       <c r="R12" t="n">
-        <v>6951891</v>
+        <v>6951824</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,10 +1748,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126023934</v>
+        <v>126023926</v>
       </c>
       <c r="B13" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>482030</v>
+        <v>482123</v>
       </c>
       <c r="R13" t="n">
-        <v>6951824</v>
+        <v>6951876</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1845,10 +1845,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126023926</v>
+        <v>126023920</v>
       </c>
       <c r="B14" t="n">
-        <v>80075</v>
+        <v>78732</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1856,21 +1856,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482123</v>
+        <v>482158</v>
       </c>
       <c r="R14" t="n">
-        <v>6951876</v>
+        <v>6951891</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1945,7 +1945,7 @@
         <v>126023931</v>
       </c>
       <c r="B15" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>126023956</v>
       </c>
       <c r="B16" t="n">
-        <v>77921</v>
+        <v>77922</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>126023933</v>
       </c>
       <c r="B17" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>126023923</v>
       </c>
       <c r="B18" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2330,10 +2330,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126023946</v>
+        <v>126023921</v>
       </c>
       <c r="B19" t="n">
-        <v>78639</v>
+        <v>78732</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2341,21 +2341,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>482039</v>
+        <v>482156</v>
       </c>
       <c r="R19" t="n">
-        <v>6951778</v>
+        <v>6951883</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126023921</v>
+        <v>126023946</v>
       </c>
       <c r="B20" t="n">
-        <v>78731</v>
+        <v>78640</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>482156</v>
+        <v>482039</v>
       </c>
       <c r="R20" t="n">
-        <v>6951883</v>
+        <v>6951778</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2527,7 +2527,7 @@
         <v>126023925</v>
       </c>
       <c r="B21" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2621,57 +2621,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126023938</v>
+        <v>126023929</v>
       </c>
       <c r="B22" t="n">
-        <v>98339</v>
+        <v>80076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>482167</v>
+        <v>481977</v>
       </c>
       <c r="R22" t="n">
-        <v>6951805</v>
+        <v>6951858</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2712,7 +2700,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2731,45 +2718,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126023929</v>
+        <v>126023938</v>
       </c>
       <c r="B23" t="n">
-        <v>80075</v>
+        <v>98341</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481977</v>
+        <v>482167</v>
       </c>
       <c r="R23" t="n">
-        <v>6951858</v>
+        <v>6951805</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2810,6 +2809,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2831,7 +2831,7 @@
         <v>126023958</v>
       </c>
       <c r="B24" t="n">
-        <v>77921</v>
+        <v>77922</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>126023922</v>
       </c>
       <c r="B25" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>126023947</v>
       </c>
       <c r="B26" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126023939</v>
+        <v>126023924</v>
       </c>
       <c r="B27" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3130,21 +3130,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>482162</v>
+        <v>482164</v>
       </c>
       <c r="R27" t="n">
-        <v>6951763</v>
+        <v>6951793</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126023924</v>
+        <v>126023939</v>
       </c>
       <c r="B28" t="n">
-        <v>80075</v>
+        <v>78973</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3227,21 +3227,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>482164</v>
+        <v>482162</v>
       </c>
       <c r="R28" t="n">
-        <v>6951793</v>
+        <v>6951763</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3316,7 +3316,7 @@
         <v>126023928</v>
       </c>
       <c r="B29" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>126023937</v>
       </c>
       <c r="B30" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126023949</v>
+        <v>126023950</v>
       </c>
       <c r="B4" t="n">
-        <v>79562</v>
+        <v>78379</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,6 +948,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -966,10 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126023950</v>
+        <v>126023949</v>
       </c>
       <c r="B5" t="n">
-        <v>78379</v>
+        <v>79562</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,7 +1046,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1452,50 +1452,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126023914</v>
+        <v>126023940</v>
       </c>
       <c r="B10" t="n">
-        <v>56844</v>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482148</v>
+        <v>482101</v>
       </c>
       <c r="R10" t="n">
-        <v>6951652</v>
+        <v>6951693</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1554,45 +1549,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126023940</v>
+        <v>126023914</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>56844</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482101</v>
+        <v>482148</v>
       </c>
       <c r="R11" t="n">
-        <v>6951693</v>
+        <v>6951652</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126023916</v>
+        <v>126023949</v>
       </c>
       <c r="B3" t="n">
-        <v>80105</v>
+        <v>79562</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482137</v>
+        <v>482058</v>
       </c>
       <c r="R3" t="n">
-        <v>6951852</v>
+        <v>6951794</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -967,32 +967,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126023949</v>
+        <v>126023916</v>
       </c>
       <c r="B5" t="n">
-        <v>79562</v>
+        <v>80105</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482058</v>
+        <v>482137</v>
       </c>
       <c r="R5" t="n">
-        <v>6951794</v>
+        <v>6951852</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1161,32 +1161,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126023917</v>
+        <v>126023927</v>
       </c>
       <c r="B7" t="n">
-        <v>80104</v>
+        <v>80076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482039</v>
+        <v>482136</v>
       </c>
       <c r="R7" t="n">
-        <v>6951802</v>
+        <v>6951838</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,32 +1258,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126023927</v>
+        <v>126023917</v>
       </c>
       <c r="B8" t="n">
-        <v>80076</v>
+        <v>80104</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482136</v>
+        <v>482039</v>
       </c>
       <c r="R8" t="n">
-        <v>6951838</v>
+        <v>6951802</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126023956</v>
+        <v>126023933</v>
       </c>
       <c r="B16" t="n">
-        <v>77922</v>
+        <v>80076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2050,21 +2050,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>482150</v>
+        <v>482027</v>
       </c>
       <c r="R16" t="n">
-        <v>6951653</v>
+        <v>6951842</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2136,10 +2136,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126023933</v>
+        <v>126023956</v>
       </c>
       <c r="B17" t="n">
-        <v>80076</v>
+        <v>77922</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2147,21 +2147,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>482027</v>
+        <v>482150</v>
       </c>
       <c r="R17" t="n">
-        <v>6951842</v>
+        <v>6951653</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2330,10 +2330,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126023921</v>
+        <v>126023946</v>
       </c>
       <c r="B19" t="n">
-        <v>78732</v>
+        <v>78640</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2341,21 +2341,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>482156</v>
+        <v>482039</v>
       </c>
       <c r="R19" t="n">
-        <v>6951883</v>
+        <v>6951778</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126023946</v>
+        <v>126023921</v>
       </c>
       <c r="B20" t="n">
-        <v>78640</v>
+        <v>78732</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>482039</v>
+        <v>482156</v>
       </c>
       <c r="R20" t="n">
-        <v>6951778</v>
+        <v>6951883</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2721,7 +2721,7 @@
         <v>126023938</v>
       </c>
       <c r="B23" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126023924</v>
+        <v>126023939</v>
       </c>
       <c r="B27" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3130,21 +3130,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>482164</v>
+        <v>482162</v>
       </c>
       <c r="R27" t="n">
-        <v>6951793</v>
+        <v>6951763</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126023939</v>
+        <v>126023924</v>
       </c>
       <c r="B28" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3227,21 +3227,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>482162</v>
+        <v>482164</v>
       </c>
       <c r="R28" t="n">
-        <v>6951763</v>
+        <v>6951793</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126023949</v>
+        <v>126023950</v>
       </c>
       <c r="B3" t="n">
-        <v>79562</v>
+        <v>78379</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -851,6 +851,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -869,32 +870,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126023950</v>
+        <v>126023916</v>
       </c>
       <c r="B4" t="n">
-        <v>78379</v>
+        <v>80105</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482058</v>
+        <v>482137</v>
       </c>
       <c r="R4" t="n">
-        <v>6951794</v>
+        <v>6951852</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,7 +949,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -967,32 +967,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126023916</v>
+        <v>126023949</v>
       </c>
       <c r="B5" t="n">
-        <v>80105</v>
+        <v>79562</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482137</v>
+        <v>482058</v>
       </c>
       <c r="R5" t="n">
-        <v>6951852</v>
+        <v>6951794</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1161,32 +1161,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126023927</v>
+        <v>126023917</v>
       </c>
       <c r="B7" t="n">
-        <v>80076</v>
+        <v>80104</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482136</v>
+        <v>482039</v>
       </c>
       <c r="R7" t="n">
-        <v>6951838</v>
+        <v>6951802</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,32 +1258,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126023917</v>
+        <v>126023927</v>
       </c>
       <c r="B8" t="n">
-        <v>80104</v>
+        <v>80076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482039</v>
+        <v>482136</v>
       </c>
       <c r="R8" t="n">
-        <v>6951802</v>
+        <v>6951838</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126023947</v>
+        <v>126023924</v>
       </c>
       <c r="B26" t="n">
-        <v>78640</v>
+        <v>80076</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>482066</v>
+        <v>482164</v>
       </c>
       <c r="R26" t="n">
-        <v>6951791</v>
+        <v>6951793</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126023939</v>
+        <v>126023947</v>
       </c>
       <c r="B27" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3130,21 +3130,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>482162</v>
+        <v>482066</v>
       </c>
       <c r="R27" t="n">
-        <v>6951763</v>
+        <v>6951791</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126023924</v>
+        <v>126023939</v>
       </c>
       <c r="B28" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3227,21 +3227,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>482164</v>
+        <v>482162</v>
       </c>
       <c r="R28" t="n">
-        <v>6951793</v>
+        <v>6951763</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -870,32 +870,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126023916</v>
+        <v>126023949</v>
       </c>
       <c r="B4" t="n">
-        <v>80105</v>
+        <v>79562</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482137</v>
+        <v>482058</v>
       </c>
       <c r="R4" t="n">
-        <v>6951852</v>
+        <v>6951794</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,32 +967,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126023949</v>
+        <v>126023916</v>
       </c>
       <c r="B5" t="n">
-        <v>79562</v>
+        <v>80105</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482058</v>
+        <v>482137</v>
       </c>
       <c r="R5" t="n">
-        <v>6951794</v>
+        <v>6951852</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1452,45 +1452,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126023940</v>
+        <v>126023914</v>
       </c>
       <c r="B10" t="n">
-        <v>78973</v>
+        <v>56844</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482101</v>
+        <v>482148</v>
       </c>
       <c r="R10" t="n">
-        <v>6951693</v>
+        <v>6951652</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,50 +1554,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126023914</v>
+        <v>126023940</v>
       </c>
       <c r="B11" t="n">
-        <v>56844</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482148</v>
+        <v>482101</v>
       </c>
       <c r="R11" t="n">
-        <v>6951652</v>
+        <v>6951693</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126023934</v>
+        <v>126023920</v>
       </c>
       <c r="B12" t="n">
-        <v>80076</v>
+        <v>78732</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1662,21 +1662,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482030</v>
+        <v>482158</v>
       </c>
       <c r="R12" t="n">
-        <v>6951824</v>
+        <v>6951891</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,7 +1748,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126023926</v>
+        <v>126023934</v>
       </c>
       <c r="B13" t="n">
         <v>80076</v>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>482123</v>
+        <v>482030</v>
       </c>
       <c r="R13" t="n">
-        <v>6951876</v>
+        <v>6951824</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1845,10 +1845,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126023920</v>
+        <v>126023926</v>
       </c>
       <c r="B14" t="n">
-        <v>78732</v>
+        <v>80076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1856,21 +1856,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482158</v>
+        <v>482123</v>
       </c>
       <c r="R14" t="n">
-        <v>6951891</v>
+        <v>6951876</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2330,10 +2330,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126023946</v>
+        <v>126023921</v>
       </c>
       <c r="B19" t="n">
-        <v>78640</v>
+        <v>78732</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2341,21 +2341,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>482039</v>
+        <v>482156</v>
       </c>
       <c r="R19" t="n">
-        <v>6951778</v>
+        <v>6951883</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126023921</v>
+        <v>126023946</v>
       </c>
       <c r="B20" t="n">
-        <v>78732</v>
+        <v>78640</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>482156</v>
+        <v>482039</v>
       </c>
       <c r="R20" t="n">
-        <v>6951883</v>
+        <v>6951778</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2721,7 +2721,7 @@
         <v>126023938</v>
       </c>
       <c r="B23" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126023924</v>
+        <v>126023947</v>
       </c>
       <c r="B26" t="n">
-        <v>80076</v>
+        <v>78640</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>482164</v>
+        <v>482066</v>
       </c>
       <c r="R26" t="n">
-        <v>6951793</v>
+        <v>6951791</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126023947</v>
+        <v>126023939</v>
       </c>
       <c r="B27" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3130,21 +3130,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>482066</v>
+        <v>482162</v>
       </c>
       <c r="R27" t="n">
-        <v>6951791</v>
+        <v>6951763</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126023939</v>
+        <v>126023924</v>
       </c>
       <c r="B28" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3227,21 +3227,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>482162</v>
+        <v>482164</v>
       </c>
       <c r="R28" t="n">
-        <v>6951763</v>
+        <v>6951793</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -1452,50 +1452,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126023914</v>
+        <v>126023940</v>
       </c>
       <c r="B10" t="n">
-        <v>56844</v>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482148</v>
+        <v>482101</v>
       </c>
       <c r="R10" t="n">
-        <v>6951652</v>
+        <v>6951693</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1554,45 +1549,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126023940</v>
+        <v>126023914</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>56844</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482101</v>
+        <v>482148</v>
       </c>
       <c r="R11" t="n">
-        <v>6951693</v>
+        <v>6951652</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126023920</v>
+        <v>126023934</v>
       </c>
       <c r="B12" t="n">
-        <v>78732</v>
+        <v>80076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1662,21 +1662,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482158</v>
+        <v>482030</v>
       </c>
       <c r="R12" t="n">
-        <v>6951891</v>
+        <v>6951824</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,7 +1748,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126023934</v>
+        <v>126023926</v>
       </c>
       <c r="B13" t="n">
         <v>80076</v>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>482030</v>
+        <v>482123</v>
       </c>
       <c r="R13" t="n">
-        <v>6951824</v>
+        <v>6951876</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1845,10 +1845,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126023926</v>
+        <v>126023920</v>
       </c>
       <c r="B14" t="n">
-        <v>80076</v>
+        <v>78732</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1856,21 +1856,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482123</v>
+        <v>482158</v>
       </c>
       <c r="R14" t="n">
-        <v>6951876</v>
+        <v>6951891</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126023947</v>
+        <v>126023939</v>
       </c>
       <c r="B26" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>482066</v>
+        <v>482162</v>
       </c>
       <c r="R26" t="n">
-        <v>6951791</v>
+        <v>6951763</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126023939</v>
+        <v>126023924</v>
       </c>
       <c r="B27" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3130,21 +3130,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>482162</v>
+        <v>482164</v>
       </c>
       <c r="R27" t="n">
-        <v>6951763</v>
+        <v>6951793</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126023924</v>
+        <v>126023947</v>
       </c>
       <c r="B28" t="n">
-        <v>80076</v>
+        <v>78640</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3227,21 +3227,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>482164</v>
+        <v>482066</v>
       </c>
       <c r="R28" t="n">
-        <v>6951793</v>
+        <v>6951791</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126023941</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126023950</v>
       </c>
       <c r="B3" t="n">
-        <v>78379</v>
+        <v>78383</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -870,32 +870,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126023949</v>
+        <v>126023916</v>
       </c>
       <c r="B4" t="n">
-        <v>79562</v>
+        <v>80109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482058</v>
+        <v>482137</v>
       </c>
       <c r="R4" t="n">
-        <v>6951794</v>
+        <v>6951852</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,32 +967,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126023916</v>
+        <v>126023949</v>
       </c>
       <c r="B5" t="n">
-        <v>80105</v>
+        <v>79566</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482137</v>
+        <v>482058</v>
       </c>
       <c r="R5" t="n">
-        <v>6951852</v>
+        <v>6951794</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,7 +1067,7 @@
         <v>126023932</v>
       </c>
       <c r="B6" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,32 +1161,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126023917</v>
+        <v>126023927</v>
       </c>
       <c r="B7" t="n">
-        <v>80104</v>
+        <v>80080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482039</v>
+        <v>482136</v>
       </c>
       <c r="R7" t="n">
-        <v>6951802</v>
+        <v>6951838</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,32 +1258,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126023927</v>
+        <v>126023917</v>
       </c>
       <c r="B8" t="n">
-        <v>80076</v>
+        <v>80108</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482136</v>
+        <v>482039</v>
       </c>
       <c r="R8" t="n">
-        <v>6951838</v>
+        <v>6951802</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1358,7 +1358,7 @@
         <v>126023948</v>
       </c>
       <c r="B9" t="n">
-        <v>77922</v>
+        <v>77926</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1452,45 +1452,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126023940</v>
+        <v>126023914</v>
       </c>
       <c r="B10" t="n">
-        <v>78973</v>
+        <v>56848</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482101</v>
+        <v>482148</v>
       </c>
       <c r="R10" t="n">
-        <v>6951693</v>
+        <v>6951652</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,50 +1554,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126023914</v>
+        <v>126023940</v>
       </c>
       <c r="B11" t="n">
-        <v>56844</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482148</v>
+        <v>482101</v>
       </c>
       <c r="R11" t="n">
-        <v>6951652</v>
+        <v>6951693</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,7 +1654,7 @@
         <v>126023934</v>
       </c>
       <c r="B12" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>126023926</v>
       </c>
       <c r="B13" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>126023920</v>
       </c>
       <c r="B14" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>126023931</v>
       </c>
       <c r="B15" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>126023933</v>
       </c>
       <c r="B16" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>126023956</v>
       </c>
       <c r="B17" t="n">
-        <v>77922</v>
+        <v>77926</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>126023923</v>
       </c>
       <c r="B18" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2330,10 +2330,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126023921</v>
+        <v>126023946</v>
       </c>
       <c r="B19" t="n">
-        <v>78732</v>
+        <v>78644</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2341,21 +2341,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>482156</v>
+        <v>482039</v>
       </c>
       <c r="R19" t="n">
-        <v>6951883</v>
+        <v>6951778</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126023946</v>
+        <v>126023921</v>
       </c>
       <c r="B20" t="n">
-        <v>78640</v>
+        <v>78736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>482039</v>
+        <v>482156</v>
       </c>
       <c r="R20" t="n">
-        <v>6951778</v>
+        <v>6951883</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2527,7 +2527,7 @@
         <v>126023925</v>
       </c>
       <c r="B21" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>126023929</v>
       </c>
       <c r="B22" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>126023938</v>
       </c>
       <c r="B23" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>126023958</v>
       </c>
       <c r="B24" t="n">
-        <v>77922</v>
+        <v>77926</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>126023922</v>
       </c>
       <c r="B25" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126023939</v>
+        <v>126023947</v>
       </c>
       <c r="B26" t="n">
-        <v>78973</v>
+        <v>78644</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>482162</v>
+        <v>482066</v>
       </c>
       <c r="R26" t="n">
-        <v>6951763</v>
+        <v>6951791</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3122,7 +3122,7 @@
         <v>126023924</v>
       </c>
       <c r="B27" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126023947</v>
+        <v>126023939</v>
       </c>
       <c r="B28" t="n">
-        <v>78640</v>
+        <v>78977</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3227,21 +3227,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>482066</v>
+        <v>482162</v>
       </c>
       <c r="R28" t="n">
-        <v>6951791</v>
+        <v>6951763</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3316,7 +3316,7 @@
         <v>126023928</v>
       </c>
       <c r="B29" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>126023937</v>
       </c>
       <c r="B30" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -2330,10 +2330,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126023946</v>
+        <v>126023921</v>
       </c>
       <c r="B19" t="n">
-        <v>78644</v>
+        <v>78736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2341,21 +2341,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>482039</v>
+        <v>482156</v>
       </c>
       <c r="R19" t="n">
-        <v>6951778</v>
+        <v>6951883</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126023921</v>
+        <v>126023946</v>
       </c>
       <c r="B20" t="n">
-        <v>78736</v>
+        <v>78644</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>482156</v>
+        <v>482039</v>
       </c>
       <c r="R20" t="n">
-        <v>6951883</v>
+        <v>6951778</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -1161,32 +1161,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126023927</v>
+        <v>126023917</v>
       </c>
       <c r="B7" t="n">
-        <v>80080</v>
+        <v>80108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482136</v>
+        <v>482039</v>
       </c>
       <c r="R7" t="n">
-        <v>6951838</v>
+        <v>6951802</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,32 +1258,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126023917</v>
+        <v>126023927</v>
       </c>
       <c r="B8" t="n">
-        <v>80108</v>
+        <v>80080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482039</v>
+        <v>482136</v>
       </c>
       <c r="R8" t="n">
-        <v>6951802</v>
+        <v>6951838</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,50 +1452,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126023914</v>
+        <v>126023940</v>
       </c>
       <c r="B10" t="n">
-        <v>56848</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482148</v>
+        <v>482101</v>
       </c>
       <c r="R10" t="n">
-        <v>6951652</v>
+        <v>6951693</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1554,45 +1549,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126023940</v>
+        <v>126023914</v>
       </c>
       <c r="B11" t="n">
-        <v>78977</v>
+        <v>56848</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482101</v>
+        <v>482148</v>
       </c>
       <c r="R11" t="n">
-        <v>6951693</v>
+        <v>6951652</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2721,7 +2721,7 @@
         <v>126023938</v>
       </c>
       <c r="B23" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126023947</v>
+        <v>126023924</v>
       </c>
       <c r="B26" t="n">
-        <v>78644</v>
+        <v>80080</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>482066</v>
+        <v>482164</v>
       </c>
       <c r="R26" t="n">
-        <v>6951791</v>
+        <v>6951793</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126023924</v>
+        <v>126023939</v>
       </c>
       <c r="B27" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3130,21 +3130,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>482164</v>
+        <v>482162</v>
       </c>
       <c r="R27" t="n">
-        <v>6951793</v>
+        <v>6951763</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126023939</v>
+        <v>126023947</v>
       </c>
       <c r="B28" t="n">
-        <v>78977</v>
+        <v>78644</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3227,21 +3227,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>482162</v>
+        <v>482066</v>
       </c>
       <c r="R28" t="n">
-        <v>6951763</v>
+        <v>6951791</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -2524,45 +2524,57 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126023925</v>
+        <v>126023938</v>
       </c>
       <c r="B21" t="n">
-        <v>80080</v>
+        <v>98352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>482111</v>
+        <v>482167</v>
       </c>
       <c r="R21" t="n">
-        <v>6951916</v>
+        <v>6951805</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2603,6 +2615,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2621,7 +2634,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126023929</v>
+        <v>126023925</v>
       </c>
       <c r="B22" t="n">
         <v>80080</v>
@@ -2656,10 +2669,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481977</v>
+        <v>482111</v>
       </c>
       <c r="R22" t="n">
-        <v>6951858</v>
+        <v>6951916</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2718,57 +2731,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126023938</v>
+        <v>126023929</v>
       </c>
       <c r="B23" t="n">
-        <v>98352</v>
+        <v>80080</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>482167</v>
+        <v>481977</v>
       </c>
       <c r="R23" t="n">
-        <v>6951805</v>
+        <v>6951858</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,7 +2810,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126023950</v>
+        <v>126023916</v>
       </c>
       <c r="B3" t="n">
-        <v>78383</v>
+        <v>80109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482058</v>
+        <v>482137</v>
       </c>
       <c r="R3" t="n">
-        <v>6951794</v>
+        <v>6951852</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -870,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126023916</v>
+        <v>126023949</v>
       </c>
       <c r="B4" t="n">
-        <v>80109</v>
+        <v>79566</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -905,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482137</v>
+        <v>482058</v>
       </c>
       <c r="R4" t="n">
-        <v>6951852</v>
+        <v>6951794</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126023949</v>
+        <v>126023950</v>
       </c>
       <c r="B5" t="n">
-        <v>79566</v>
+        <v>78383</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -978,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,6 +1045,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126023934</v>
+        <v>126023920</v>
       </c>
       <c r="B12" t="n">
-        <v>80080</v>
+        <v>78736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1662,21 +1662,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482030</v>
+        <v>482158</v>
       </c>
       <c r="R12" t="n">
-        <v>6951824</v>
+        <v>6951891</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,7 +1748,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126023926</v>
+        <v>126023934</v>
       </c>
       <c r="B13" t="n">
         <v>80080</v>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>482123</v>
+        <v>482030</v>
       </c>
       <c r="R13" t="n">
-        <v>6951876</v>
+        <v>6951824</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1845,10 +1845,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126023920</v>
+        <v>126023926</v>
       </c>
       <c r="B14" t="n">
-        <v>78736</v>
+        <v>80080</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1856,21 +1856,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482158</v>
+        <v>482123</v>
       </c>
       <c r="R14" t="n">
-        <v>6951891</v>
+        <v>6951876</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2330,10 +2330,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126023921</v>
+        <v>126023946</v>
       </c>
       <c r="B19" t="n">
-        <v>78736</v>
+        <v>78644</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2341,21 +2341,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>482156</v>
+        <v>482039</v>
       </c>
       <c r="R19" t="n">
-        <v>6951883</v>
+        <v>6951778</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126023946</v>
+        <v>126023921</v>
       </c>
       <c r="B20" t="n">
-        <v>78644</v>
+        <v>78736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>482039</v>
+        <v>482156</v>
       </c>
       <c r="R20" t="n">
-        <v>6951778</v>
+        <v>6951883</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126023924</v>
+        <v>126023939</v>
       </c>
       <c r="B26" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>482164</v>
+        <v>482162</v>
       </c>
       <c r="R26" t="n">
-        <v>6951793</v>
+        <v>6951763</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126023939</v>
+        <v>126023947</v>
       </c>
       <c r="B27" t="n">
-        <v>78977</v>
+        <v>78644</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3130,21 +3130,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>482162</v>
+        <v>482066</v>
       </c>
       <c r="R27" t="n">
-        <v>6951763</v>
+        <v>6951791</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126023947</v>
+        <v>126023924</v>
       </c>
       <c r="B28" t="n">
-        <v>78644</v>
+        <v>80080</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3227,21 +3227,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>482066</v>
+        <v>482164</v>
       </c>
       <c r="R28" t="n">
-        <v>6951791</v>
+        <v>6951793</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126023949</v>
+        <v>126023950</v>
       </c>
       <c r="B4" t="n">
-        <v>79566</v>
+        <v>78383</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,6 +948,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -966,10 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126023950</v>
+        <v>126023949</v>
       </c>
       <c r="B5" t="n">
-        <v>78383</v>
+        <v>79566</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,7 +1046,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -2524,57 +2524,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126023938</v>
+        <v>126023925</v>
       </c>
       <c r="B21" t="n">
-        <v>98352</v>
+        <v>80080</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>482167</v>
+        <v>482111</v>
       </c>
       <c r="R21" t="n">
-        <v>6951805</v>
+        <v>6951916</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2615,7 +2603,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2634,7 +2621,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126023925</v>
+        <v>126023929</v>
       </c>
       <c r="B22" t="n">
         <v>80080</v>
@@ -2669,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>482111</v>
+        <v>481977</v>
       </c>
       <c r="R22" t="n">
-        <v>6951916</v>
+        <v>6951858</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2731,45 +2718,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126023929</v>
+        <v>126023938</v>
       </c>
       <c r="B23" t="n">
-        <v>80080</v>
+        <v>98352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481977</v>
+        <v>482167</v>
       </c>
       <c r="R23" t="n">
-        <v>6951858</v>
+        <v>6951805</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2810,6 +2809,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126023941</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126023916</v>
+        <v>126023950</v>
       </c>
       <c r="B3" t="n">
-        <v>80109</v>
+        <v>78386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482137</v>
+        <v>482058</v>
       </c>
       <c r="R3" t="n">
-        <v>6951852</v>
+        <v>6951794</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,6 +851,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -869,32 +870,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126023950</v>
+        <v>126023916</v>
       </c>
       <c r="B4" t="n">
-        <v>78383</v>
+        <v>80112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482058</v>
+        <v>482137</v>
       </c>
       <c r="R4" t="n">
-        <v>6951794</v>
+        <v>6951852</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,7 +949,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -970,7 +970,7 @@
         <v>126023949</v>
       </c>
       <c r="B5" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>126023932</v>
       </c>
       <c r="B6" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>126023917</v>
       </c>
       <c r="B7" t="n">
-        <v>80108</v>
+        <v>80111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>126023927</v>
       </c>
       <c r="B8" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>126023948</v>
       </c>
       <c r="B9" t="n">
-        <v>77926</v>
+        <v>77929</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>126023940</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>126023914</v>
       </c>
       <c r="B11" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126023920</v>
+        <v>126023934</v>
       </c>
       <c r="B12" t="n">
-        <v>78736</v>
+        <v>80083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1662,21 +1662,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482158</v>
+        <v>482030</v>
       </c>
       <c r="R12" t="n">
-        <v>6951891</v>
+        <v>6951824</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,10 +1748,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126023934</v>
+        <v>126023926</v>
       </c>
       <c r="B13" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>482030</v>
+        <v>482123</v>
       </c>
       <c r="R13" t="n">
-        <v>6951824</v>
+        <v>6951876</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1845,10 +1845,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126023926</v>
+        <v>126023920</v>
       </c>
       <c r="B14" t="n">
-        <v>80080</v>
+        <v>78739</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1856,21 +1856,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482123</v>
+        <v>482158</v>
       </c>
       <c r="R14" t="n">
-        <v>6951876</v>
+        <v>6951891</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1945,7 +1945,7 @@
         <v>126023931</v>
       </c>
       <c r="B15" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>126023933</v>
       </c>
       <c r="B16" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>126023956</v>
       </c>
       <c r="B17" t="n">
-        <v>77926</v>
+        <v>77929</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>126023923</v>
       </c>
       <c r="B18" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>126023946</v>
       </c>
       <c r="B19" t="n">
-        <v>78644</v>
+        <v>78647</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>126023921</v>
       </c>
       <c r="B20" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2524,45 +2524,57 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126023925</v>
+        <v>126023938</v>
       </c>
       <c r="B21" t="n">
-        <v>80080</v>
+        <v>98361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>482111</v>
+        <v>482167</v>
       </c>
       <c r="R21" t="n">
-        <v>6951916</v>
+        <v>6951805</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2603,6 +2615,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2621,10 +2634,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126023929</v>
+        <v>126023925</v>
       </c>
       <c r="B22" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2656,10 +2669,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481977</v>
+        <v>482111</v>
       </c>
       <c r="R22" t="n">
-        <v>6951858</v>
+        <v>6951916</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2718,57 +2731,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126023938</v>
+        <v>126023929</v>
       </c>
       <c r="B23" t="n">
-        <v>98352</v>
+        <v>80083</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>482167</v>
+        <v>481977</v>
       </c>
       <c r="R23" t="n">
-        <v>6951805</v>
+        <v>6951858</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,7 +2810,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2831,7 +2831,7 @@
         <v>126023958</v>
       </c>
       <c r="B24" t="n">
-        <v>77926</v>
+        <v>77929</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>126023922</v>
       </c>
       <c r="B25" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126023939</v>
+        <v>126023947</v>
       </c>
       <c r="B26" t="n">
-        <v>78977</v>
+        <v>78647</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>482162</v>
+        <v>482066</v>
       </c>
       <c r="R26" t="n">
-        <v>6951763</v>
+        <v>6951791</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126023947</v>
+        <v>126023924</v>
       </c>
       <c r="B27" t="n">
-        <v>78644</v>
+        <v>80083</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3130,21 +3130,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>482066</v>
+        <v>482164</v>
       </c>
       <c r="R27" t="n">
-        <v>6951791</v>
+        <v>6951793</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126023924</v>
+        <v>126023939</v>
       </c>
       <c r="B28" t="n">
-        <v>80080</v>
+        <v>78980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3227,21 +3227,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>482164</v>
+        <v>482162</v>
       </c>
       <c r="R28" t="n">
-        <v>6951793</v>
+        <v>6951763</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3316,7 +3316,7 @@
         <v>126023928</v>
       </c>
       <c r="B29" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>126023937</v>
       </c>
       <c r="B30" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126023950</v>
+        <v>126023916</v>
       </c>
       <c r="B3" t="n">
-        <v>78386</v>
+        <v>80112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482058</v>
+        <v>482137</v>
       </c>
       <c r="R3" t="n">
-        <v>6951794</v>
+        <v>6951852</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -870,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126023916</v>
+        <v>126023950</v>
       </c>
       <c r="B4" t="n">
-        <v>80112</v>
+        <v>78386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -905,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482137</v>
+        <v>482058</v>
       </c>
       <c r="R4" t="n">
-        <v>6951852</v>
+        <v>6951794</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,6 +948,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -2524,57 +2524,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126023938</v>
+        <v>126023925</v>
       </c>
       <c r="B21" t="n">
-        <v>98361</v>
+        <v>80083</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>482167</v>
+        <v>482111</v>
       </c>
       <c r="R21" t="n">
-        <v>6951805</v>
+        <v>6951916</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2615,7 +2603,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2634,7 +2621,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126023925</v>
+        <v>126023929</v>
       </c>
       <c r="B22" t="n">
         <v>80083</v>
@@ -2669,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>482111</v>
+        <v>481977</v>
       </c>
       <c r="R22" t="n">
-        <v>6951916</v>
+        <v>6951858</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2731,45 +2718,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126023929</v>
+        <v>126023938</v>
       </c>
       <c r="B23" t="n">
-        <v>80083</v>
+        <v>98361</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481977</v>
+        <v>482167</v>
       </c>
       <c r="R23" t="n">
-        <v>6951858</v>
+        <v>6951805</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2810,6 +2809,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126023947</v>
+        <v>126023939</v>
       </c>
       <c r="B26" t="n">
-        <v>78647</v>
+        <v>78980</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>482066</v>
+        <v>482162</v>
       </c>
       <c r="R26" t="n">
-        <v>6951791</v>
+        <v>6951763</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126023924</v>
+        <v>126023947</v>
       </c>
       <c r="B27" t="n">
-        <v>80083</v>
+        <v>78647</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3130,21 +3130,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>482164</v>
+        <v>482066</v>
       </c>
       <c r="R27" t="n">
-        <v>6951793</v>
+        <v>6951791</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126023939</v>
+        <v>126023924</v>
       </c>
       <c r="B28" t="n">
-        <v>78980</v>
+        <v>80083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3227,21 +3227,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>482162</v>
+        <v>482164</v>
       </c>
       <c r="R28" t="n">
-        <v>6951763</v>
+        <v>6951793</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -3022,10 +3022,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126023939</v>
+        <v>126023947</v>
       </c>
       <c r="B26" t="n">
-        <v>78980</v>
+        <v>78647</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>482162</v>
+        <v>482066</v>
       </c>
       <c r="R26" t="n">
-        <v>6951763</v>
+        <v>6951791</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126023947</v>
+        <v>126023939</v>
       </c>
       <c r="B27" t="n">
-        <v>78647</v>
+        <v>78980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3130,21 +3130,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>482066</v>
+        <v>482162</v>
       </c>
       <c r="R27" t="n">
-        <v>6951791</v>
+        <v>6951763</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126023916</v>
+        <v>126023950</v>
       </c>
       <c r="B3" t="n">
-        <v>80112</v>
+        <v>78386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482137</v>
+        <v>482058</v>
       </c>
       <c r="R3" t="n">
-        <v>6951852</v>
+        <v>6951794</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,6 +851,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -869,32 +870,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126023950</v>
+        <v>126023916</v>
       </c>
       <c r="B4" t="n">
-        <v>78386</v>
+        <v>80112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482058</v>
+        <v>482137</v>
       </c>
       <c r="R4" t="n">
-        <v>6951794</v>
+        <v>6951852</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,7 +949,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -1651,10 +1651,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126023934</v>
+        <v>126023920</v>
       </c>
       <c r="B12" t="n">
-        <v>80083</v>
+        <v>78739</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1662,21 +1662,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482030</v>
+        <v>482158</v>
       </c>
       <c r="R12" t="n">
-        <v>6951824</v>
+        <v>6951891</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,7 +1748,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126023926</v>
+        <v>126023934</v>
       </c>
       <c r="B13" t="n">
         <v>80083</v>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>482123</v>
+        <v>482030</v>
       </c>
       <c r="R13" t="n">
-        <v>6951876</v>
+        <v>6951824</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1845,10 +1845,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126023920</v>
+        <v>126023926</v>
       </c>
       <c r="B14" t="n">
-        <v>78739</v>
+        <v>80083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1856,21 +1856,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482158</v>
+        <v>482123</v>
       </c>
       <c r="R14" t="n">
-        <v>6951891</v>
+        <v>6951876</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126023947</v>
+        <v>126023939</v>
       </c>
       <c r="B26" t="n">
-        <v>78647</v>
+        <v>78980</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>482066</v>
+        <v>482162</v>
       </c>
       <c r="R26" t="n">
-        <v>6951791</v>
+        <v>6951763</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126023939</v>
+        <v>126023947</v>
       </c>
       <c r="B27" t="n">
-        <v>78980</v>
+        <v>78647</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3130,21 +3130,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>482162</v>
+        <v>482066</v>
       </c>
       <c r="R27" t="n">
-        <v>6951763</v>
+        <v>6951791</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3505,6 +3505,112 @@
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128159831</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>482064</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6951876</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Flera lunglavsklädda sälgar.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -3510,7 +3510,7 @@
         <v>128159831</v>
       </c>
       <c r="B31" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -3510,7 +3510,7 @@
         <v>128159831</v>
       </c>
       <c r="B31" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -3510,7 +3510,7 @@
         <v>128159831</v>
       </c>
       <c r="B31" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -3510,7 +3510,7 @@
         <v>128159831</v>
       </c>
       <c r="B31" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126023941</v>
+        <v>126023945</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482047</v>
+        <v>482187</v>
       </c>
       <c r="R2" t="n">
-        <v>6951803</v>
+        <v>6951940</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126023950</v>
+        <v>126023946</v>
       </c>
       <c r="B3" t="n">
-        <v>78386</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482058</v>
+        <v>482039</v>
       </c>
       <c r="R3" t="n">
-        <v>6951794</v>
+        <v>6951778</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -870,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126023916</v>
+        <v>126023947</v>
       </c>
       <c r="B4" t="n">
-        <v>80112</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -905,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482137</v>
+        <v>482066</v>
       </c>
       <c r="R4" t="n">
-        <v>6951852</v>
+        <v>6951791</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126023949</v>
+        <v>126023939</v>
       </c>
       <c r="B5" t="n">
-        <v>79569</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482058</v>
+        <v>482162</v>
       </c>
       <c r="R5" t="n">
-        <v>6951794</v>
+        <v>6951763</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126023932</v>
+        <v>126023940</v>
       </c>
       <c r="B6" t="n">
-        <v>80083</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482012</v>
+        <v>482101</v>
       </c>
       <c r="R6" t="n">
-        <v>6951841</v>
+        <v>6951693</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126023917</v>
+        <v>126023941</v>
       </c>
       <c r="B7" t="n">
-        <v>80111</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1196,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482039</v>
+        <v>482047</v>
       </c>
       <c r="R7" t="n">
-        <v>6951802</v>
+        <v>6951803</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126023927</v>
+        <v>126023950</v>
       </c>
       <c r="B8" t="n">
-        <v>80083</v>
+        <v>78730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1269,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1293,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482136</v>
+        <v>482058</v>
       </c>
       <c r="R8" t="n">
-        <v>6951838</v>
+        <v>6951794</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1337,6 +1336,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1355,10 +1355,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126023948</v>
+        <v>126023953</v>
       </c>
       <c r="B9" t="n">
-        <v>77929</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1366,21 +1366,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482058</v>
+        <v>482210</v>
       </c>
       <c r="R9" t="n">
-        <v>6951794</v>
+        <v>6951882</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126023940</v>
+        <v>126023912</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>79946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1463,21 +1463,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482101</v>
+        <v>482212</v>
       </c>
       <c r="R10" t="n">
-        <v>6951693</v>
+        <v>6951834</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,50 +1549,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126023914</v>
+        <v>126023943</v>
       </c>
       <c r="B11" t="n">
-        <v>56849</v>
+        <v>79946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482148</v>
+        <v>482187</v>
       </c>
       <c r="R11" t="n">
-        <v>6951652</v>
+        <v>6951940</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,10 +1646,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126023934</v>
+        <v>126023923</v>
       </c>
       <c r="B12" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1686,10 +1681,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482030</v>
+        <v>482181</v>
       </c>
       <c r="R12" t="n">
-        <v>6951824</v>
+        <v>6951732</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,10 +1743,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126023926</v>
+        <v>126023924</v>
       </c>
       <c r="B13" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1783,10 +1778,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>482123</v>
+        <v>482164</v>
       </c>
       <c r="R13" t="n">
-        <v>6951876</v>
+        <v>6951793</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1845,10 +1840,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126023920</v>
+        <v>126023925</v>
       </c>
       <c r="B14" t="n">
-        <v>78739</v>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1856,21 +1851,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1880,10 +1875,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482158</v>
+        <v>482111</v>
       </c>
       <c r="R14" t="n">
-        <v>6951891</v>
+        <v>6951916</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1942,10 +1937,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126023931</v>
+        <v>126023926</v>
       </c>
       <c r="B15" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,10 +1972,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481998</v>
+        <v>482123</v>
       </c>
       <c r="R15" t="n">
-        <v>6951823</v>
+        <v>6951876</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2039,10 +2034,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126023933</v>
+        <v>126023927</v>
       </c>
       <c r="B16" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2074,10 +2069,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>482027</v>
+        <v>482136</v>
       </c>
       <c r="R16" t="n">
-        <v>6951842</v>
+        <v>6951838</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2136,10 +2131,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126023956</v>
+        <v>126023928</v>
       </c>
       <c r="B17" t="n">
-        <v>77929</v>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2147,21 +2142,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2171,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>482150</v>
+        <v>482070</v>
       </c>
       <c r="R17" t="n">
-        <v>6951653</v>
+        <v>6951872</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2233,10 +2228,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126023923</v>
+        <v>126023929</v>
       </c>
       <c r="B18" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2268,10 +2263,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>482181</v>
+        <v>481977</v>
       </c>
       <c r="R18" t="n">
-        <v>6951732</v>
+        <v>6951858</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2330,10 +2325,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126023946</v>
+        <v>126023931</v>
       </c>
       <c r="B19" t="n">
-        <v>78647</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2341,21 +2336,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2365,10 +2360,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>482039</v>
+        <v>481998</v>
       </c>
       <c r="R19" t="n">
-        <v>6951778</v>
+        <v>6951823</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2427,10 +2422,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126023921</v>
+        <v>126023932</v>
       </c>
       <c r="B20" t="n">
-        <v>78739</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2438,21 +2433,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2457,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>482156</v>
+        <v>482012</v>
       </c>
       <c r="R20" t="n">
-        <v>6951883</v>
+        <v>6951841</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2524,10 +2519,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126023925</v>
+        <v>126023933</v>
       </c>
       <c r="B21" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2559,10 +2554,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>482111</v>
+        <v>482027</v>
       </c>
       <c r="R21" t="n">
-        <v>6951916</v>
+        <v>6951842</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2621,10 +2616,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126023929</v>
+        <v>126023934</v>
       </c>
       <c r="B22" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2656,10 +2651,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481977</v>
+        <v>482030</v>
       </c>
       <c r="R22" t="n">
-        <v>6951858</v>
+        <v>6951824</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2718,57 +2713,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126023938</v>
+        <v>126023937</v>
       </c>
       <c r="B23" t="n">
-        <v>98361</v>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>482167</v>
+        <v>482050</v>
       </c>
       <c r="R23" t="n">
-        <v>6951805</v>
+        <v>6951832</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,7 +2792,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2828,10 +2810,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126023958</v>
+        <v>128159831</v>
       </c>
       <c r="B24" t="n">
-        <v>77929</v>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2839,34 +2821,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Floberget, Jmt</t>
+          <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>482044</v>
+        <v>482064</v>
       </c>
       <c r="R24" t="n">
-        <v>6951810</v>
+        <v>6951876</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2893,12 +2875,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Flera lunglavsklädda sälgar.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2913,44 +2900,48 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126023922</v>
+        <v>126023917</v>
       </c>
       <c r="B25" t="n">
-        <v>78739</v>
+        <v>80460</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2960,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>482045</v>
+        <v>482039</v>
       </c>
       <c r="R25" t="n">
-        <v>6951702</v>
+        <v>6951802</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3022,32 +3013,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126023939</v>
+        <v>126023916</v>
       </c>
       <c r="B26" t="n">
-        <v>78980</v>
+        <v>80461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3057,10 +3048,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>482162</v>
+        <v>482137</v>
       </c>
       <c r="R26" t="n">
-        <v>6951763</v>
+        <v>6951852</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3119,10 +3110,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126023947</v>
+        <v>126023948</v>
       </c>
       <c r="B27" t="n">
-        <v>78647</v>
+        <v>78334</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3130,21 +3121,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3154,10 +3145,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>482066</v>
+        <v>482058</v>
       </c>
       <c r="R27" t="n">
-        <v>6951791</v>
+        <v>6951794</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3216,10 +3207,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126023924</v>
+        <v>126023955</v>
       </c>
       <c r="B28" t="n">
-        <v>80083</v>
+        <v>78334</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3227,21 +3218,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3251,10 +3242,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>482164</v>
+        <v>482210</v>
       </c>
       <c r="R28" t="n">
-        <v>6951793</v>
+        <v>6951882</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3313,10 +3304,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126023928</v>
+        <v>126023956</v>
       </c>
       <c r="B29" t="n">
-        <v>80083</v>
+        <v>78334</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3324,21 +3315,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3348,10 +3339,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>482070</v>
+        <v>482150</v>
       </c>
       <c r="R29" t="n">
-        <v>6951872</v>
+        <v>6951653</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3410,10 +3401,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126023937</v>
+        <v>126023958</v>
       </c>
       <c r="B30" t="n">
-        <v>80083</v>
+        <v>78334</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3421,21 +3412,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3445,10 +3436,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>482050</v>
+        <v>482044</v>
       </c>
       <c r="R30" t="n">
-        <v>6951832</v>
+        <v>6951810</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3507,45 +3498,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128159831</v>
+        <v>126023914</v>
       </c>
       <c r="B31" t="n">
-        <v>80194</v>
+        <v>57141</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Näktesbergen, Jmt</t>
+          <t>Floberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>482064</v>
+        <v>482148</v>
       </c>
       <c r="R31" t="n">
-        <v>6951876</v>
+        <v>6951652</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3572,17 +3568,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Flera lunglavsklädda sälgar.</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3597,19 +3588,1110 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128159840</v>
+      </c>
+      <c r="B32" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>482223</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6951826</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
+      <c r="AX32" t="inlineStr">
         <is>
           <t>Pär Hedberg</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr">
+      <c r="AY32" t="inlineStr">
         <is>
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126023938</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Floberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>482167</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6951805</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126023918</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Floberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>482212</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6951865</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126023919</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Floberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>482210</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6951864</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126023920</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Floberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>482158</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6951891</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126023921</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Floberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>482156</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6951883</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126023922</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Floberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>482045</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6951702</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126023954</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Floberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>482210</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6951882</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126023911</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Floberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>482212</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6951834</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126023949</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Floberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>482058</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6951794</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126023951</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Floberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>482210</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6951882</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28615-2025 artfynd.xlsx
+++ b/artfynd/A 28615-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023945</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023946</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023947</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023939</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023940</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023941</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023950</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1449,6 +1489,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023953</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1546,6 +1591,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023912</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1643,6 +1693,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023943</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1740,6 +1795,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023923</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1837,6 +1897,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023924</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1934,6 +1999,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023925</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2031,6 +2101,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023926</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2128,6 +2203,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023927</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2225,6 +2305,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023928</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2322,6 +2407,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023929</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2419,6 +2509,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023931</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2516,6 +2611,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023932</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2613,6 +2713,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023933</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2710,6 +2815,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023934</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2807,6 +2917,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023937</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2913,6 +3028,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128159831</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3010,6 +3130,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023917</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3107,6 +3232,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023916</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3204,6 +3334,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023948</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3301,6 +3436,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023955</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3398,6 +3538,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023956</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3495,6 +3640,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023958</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3597,6 +3747,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023914</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3709,6 +3864,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128159840</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3819,6 +3979,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023938</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3916,6 +4081,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023918</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4013,6 +4183,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023919</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4110,6 +4285,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023920</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4207,6 +4387,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023921</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4304,6 +4489,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023922</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4401,6 +4591,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023954</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4498,6 +4693,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023911</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4595,6 +4795,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023949</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4692,8 +4897,56 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126023951</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>